--- a/docs/basic-v1.01.xlsx
+++ b/docs/basic-v1.01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CD0E02-DE4E-493D-8830-6ED49D76FFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB54881-4770-4593-AB14-18E7F751986C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3975" windowWidth="14610" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="14610" windowHeight="7845" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2758,9 +2758,6 @@
     <t>モッチに渡す道具の範囲、確認の出し方、使用量の上限に当たったときの動き</t>
   </si>
   <si>
-    <t>(Claude の案)モッチには、質問に関係する段取りさんのデータ(未完了のタスク、今週の作業時間、7日先までの予定、連絡の件数と件名)を最初にまとめて渡し、読むための道具は渡さない。操作は「タスクを足す・直す・消す」「タスクの開く先を変える」「予定を足す・直す」だけで、モッチは「やりたい操作」を返すだけにする。画面に「○○する/やめる」のボタンを出し、押されたときだけ本体が行う。メールを送る・ログインする・設定を変える・ファイルをさわる操作は渡さない。使用量の上限のときは、吹き出しに「使用量の上限のため、○時まで答えられません」と出し、話した内容は残す(エラー1と同じく、ほかの Claude の仕事も止める)</t>
-  </si>
-  <si>
     <t>S6-7</t>
   </si>
   <si>
@@ -2933,6 +2930,10 @@
   </si>
   <si>
     <t>話しかけられたとき。渡すもの:質問・今見ている画面・7日以内の会話・段取りさんのデータの要約(未完了のタスク、今週の作業時間、7日先までの予定、連絡の件数と件名)・使ってよい操作の一覧(タスクを足す・直す・消す/開く先を変える/予定を足す・直す)。返させる形:{"reply":"…","action":null|{"tool":"…","args":{…},"label":"この3つを足す"}}。action があれば画面に確認のボタンを出し、押されたときだけ本体が行う。失敗したときはエラー「モッチが答えられない」</t>
+  </si>
+  <si>
+    <t>(Claude の案を本人が確認して決定。2026-10-18)モッチには、質問に関係する段取りさんのデータ(未完了のタスク、今週の作業時間、7日先までの予定、連絡の件数と件名)を最初にまとめて渡し、読むための道具は渡さない。操作は「タスクを足す・直す・消す」「タスクの開く先を変える」「予定を足す・直す」だけで、モッチは「やりたい操作」を返すだけにする。画面に「○○する/やめる」のボタンを出し、押されたときだけ本体が行う。メールを送る・ログインする・設定を変える・ファイルをさわる操作は渡さない。使用量の上限のときは、吹き出しに「使用量の上限のため、○時まで答えられません」と出し、話した内容は残す(エラー1と同じく、ほかの Claude の仕事も止める)</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -3077,7 +3078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3125,6 +3126,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4266,8 +4270,8 @@
       <c r="C39" s="9" t="s">
         <v>809</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>810</v>
+      <c r="D39" s="21" t="s">
+        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -4985,86 +4989,86 @@
     </row>
     <row r="53" spans="1:4" ht="27">
       <c r="A53" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>811</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="9" t="s">
         <v>813</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="81">
       <c r="A54" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="C54" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>816</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>813</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="81">
       <c r="A55" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="B55" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="C55" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="D55" s="9" t="s">
         <v>820</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="27">
       <c r="A56" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="C56" s="9" t="s">
         <v>823</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="D56" s="9" t="s">
         <v>824</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="40.5">
       <c r="A57" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="C57" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="D57" s="9" t="s">
         <v>828</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27">
       <c r="A58" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="C58" s="9" t="s">
         <v>831</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="D58" s="9" t="s">
         <v>832</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -5700,14 +5704,14 @@
     <row r="47" spans="1:5" ht="27">
       <c r="A47" s="9"/>
       <c r="B47" s="9" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="27">
@@ -7466,13 +7470,13 @@
     </row>
     <row r="174" spans="1:5" ht="27">
       <c r="A174" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
       <c r="D174" s="9"/>
       <c r="E174" s="9" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -7493,7 +7497,7 @@
     <row r="176" spans="1:5">
       <c r="A176" s="9"/>
       <c r="B176" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C176" s="9" t="s">
         <v>283</v>
@@ -7502,7 +7506,7 @@
         <v>281</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -7517,46 +7521,46 @@
         <v>281</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="9"/>
       <c r="B178" s="9" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C178" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D178" s="9"/>
       <c r="E178" s="9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="27">
       <c r="A179" s="9"/>
       <c r="B179" s="9" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C179" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D179" s="9"/>
       <c r="E179" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="9"/>
       <c r="B180" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C180" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D180" s="9"/>
       <c r="E180" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -7571,7 +7575,7 @@
         <v>281</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -8244,76 +8248,76 @@
     </row>
     <row r="39" spans="1:6" ht="27">
       <c r="A39" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>848</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>849</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>355</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>850</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>851</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>853</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>854</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>350</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>856</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>857</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>368</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="27">
       <c r="A42" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>858</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>859</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>355</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
   </sheetData>
@@ -8492,26 +8496,26 @@
     </row>
     <row r="22" spans="1:2" ht="27">
       <c r="A22" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>861</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="27">
       <c r="A23" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>863</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27">
       <c r="A24" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>865</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -8626,10 +8630,10 @@
     </row>
     <row r="14" spans="1:2" ht="67.5">
       <c r="A14" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>867</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27">
